--- a/LISTAS_ORDENADAS/MI/Sogas Varillas Cables/VARILLA Y ALAMBRE VISILLO.xlsx
+++ b/LISTAS_ORDENADAS/MI/Sogas Varillas Cables/VARILLA Y ALAMBRE VISILLO.xlsx
@@ -829,13 +829,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45203.55246957178</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
+        <v>45266</v>
+      </c>
+    </row>
     <row r="6" ht="5.25" customHeight="1" s="22"/>
     <row r="7" ht="19.5" customHeight="1" s="22">
       <c r="A7" s="17" t="inlineStr">
@@ -954,16 +950,6 @@
     <row r="24" ht="18" customHeight="1" s="22">
       <c r="D24" s="5" t="n"/>
     </row>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="22">
       <c r="A35" s="11" t="inlineStr">
         <is>
@@ -1006,15 +992,12 @@
         <v>244.506</v>
       </c>
     </row>
-    <row r="39"/>
     <row r="40" ht="7.5" customHeight="1" s="22">
       <c r="A40" s="8" t="n"/>
     </row>
     <row r="41" ht="9.75" customHeight="1" s="22"/>
     <row r="42" ht="7.5" customHeight="1" s="22"/>
     <row r="43" ht="7.5" customHeight="1" s="22"/>
-    <row r="44"/>
-    <row r="45"/>
     <row r="46" ht="16.5" customHeight="1" s="22">
       <c r="A46" t="inlineStr">
         <is>
@@ -1024,9 +1007,9 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="A1:E1"/>
   </mergeCells>
